--- a/database/event/4901/event_4901_evp_summary.xlsx
+++ b/database/event/4901/event_4901_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.8488</v>
+        <v>11.807</v>
       </c>
       <c r="C2" t="n">
-        <v>7.3662</v>
+        <v>7.3402</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3653</v>
+        <v>4.26</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8488</v>
+        <v>11.807</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2126</v>
+        <v>5.1708</v>
       </c>
       <c r="G2" t="n">
         <v>6.6362</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8703</v>
+        <v>5.8048</v>
       </c>
       <c r="I2" t="n">
         <v>5.9526</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5605</v>
+        <v>6.5288</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0785</v>
+        <v>4.0588</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2289</v>
+        <v>2.1572</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5605</v>
+        <v>6.5288</v>
       </c>
       <c r="F3" t="n">
-        <v>2.848</v>
+        <v>2.8163</v>
       </c>
       <c r="G3" t="n">
         <v>3.7125</v>
       </c>
       <c r="H3" t="n">
-        <v>2.848</v>
+        <v>2.8163</v>
       </c>
       <c r="I3" t="n">
         <v>2.888</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7691</v>
+        <v>5.7495</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5865</v>
+        <v>3.5743</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9092</v>
+        <v>1.8467</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7691</v>
+        <v>5.7495</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7619</v>
+        <v>1.7422</v>
       </c>
       <c r="G4" t="n">
         <v>4.0072</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7619</v>
+        <v>1.7422</v>
       </c>
       <c r="I4" t="n">
         <v>1.7866</v>
@@ -640,7 +640,7 @@
         <v>3.2214</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6719</v>
+        <v>1.6205</v>
       </c>
       <c r="E5" t="n">
         <v>5.1817</v>
@@ -686,7 +686,7 @@
         <v>3.2114</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6655</v>
+        <v>1.6141</v>
       </c>
       <c r="E6" t="n">
         <v>5.1657</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1616</v>
+        <v>4.1416</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5872</v>
+        <v>2.5747</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2598</v>
+        <v>1.2061</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1616</v>
+        <v>4.1416</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1616</v>
+        <v>4.1416</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2224</v>
+        <v>4.1909</v>
       </c>
       <c r="I7" t="n">
         <v>4.2618</v>
@@ -778,7 +778,7 @@
         <v>2.5075</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2081</v>
+        <v>1.163</v>
       </c>
       <c r="E8" t="n">
         <v>4.0335</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9225</v>
+        <v>3.9226</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4385</v>
+        <v>2.4386</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1632</v>
+        <v>1.1189</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9225</v>
+        <v>3.9226</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0114</v>
+        <v>-0.0113</v>
       </c>
       <c r="G9" t="n">
         <v>3.9338</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0114</v>
+        <v>-0.0113</v>
       </c>
       <c r="I9" t="n">
         <v>-0.0115</v>
@@ -870,7 +870,7 @@
         <v>2.4364</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1619</v>
+        <v>1.1175</v>
       </c>
       <c r="E10" t="n">
         <v>3.9191</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8311</v>
+        <v>3.8025</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3817</v>
+        <v>2.3639</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1263</v>
+        <v>1.071</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8311</v>
+        <v>3.8025</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8311</v>
+        <v>3.8025</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8311</v>
+        <v>3.8025</v>
       </c>
       <c r="I11" t="n">
         <v>3.8668</v>
@@ -962,7 +962,7 @@
         <v>2.3191</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0856</v>
+        <v>1.0422</v>
       </c>
       <c r="E12" t="n">
         <v>3.7303</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6973</v>
+        <v>3.6787</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2985</v>
+        <v>2.287</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0723</v>
+        <v>1.0217</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6973</v>
+        <v>3.6787</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4959</v>
+        <v>2.4773</v>
       </c>
       <c r="G13" t="n">
         <v>1.2014</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4959</v>
+        <v>2.4773</v>
       </c>
       <c r="I13" t="n">
         <v>2.5192</v>
@@ -1044,277 +1044,277 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.374</v>
+        <v>3.3646</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0975</v>
+        <v>2.0917</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9417</v>
+        <v>0.8965</v>
       </c>
       <c r="E14" t="n">
-        <v>3.374</v>
+        <v>3.3646</v>
       </c>
       <c r="F14" t="n">
-        <v>3.374</v>
+        <v>4.2216</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.857</v>
       </c>
       <c r="H14" t="n">
-        <v>3.374</v>
+        <v>4.4239</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4055</v>
+        <v>3.5857</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.857</v>
       </c>
       <c r="K14" t="n">
-        <v>245</v>
+        <v>166</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4055</v>
+        <v>2.7287</v>
       </c>
       <c r="N14" t="n">
-        <v>245</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3646</v>
+        <v>3.3489</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0917</v>
+        <v>2.0819</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9379</v>
+        <v>0.8903</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3646</v>
+        <v>3.3489</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2216</v>
+        <v>3.3489</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.857</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4239</v>
+        <v>3.3489</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5857</v>
+        <v>3.4055</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.857</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7287</v>
+        <v>3.4055</v>
       </c>
       <c r="N15" t="n">
-        <v>208</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.089</v>
+        <v>3.0868</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9204</v>
+        <v>1.919</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8265</v>
+        <v>0.7859</v>
       </c>
       <c r="E16" t="n">
-        <v>3.089</v>
+        <v>3.0868</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7804</v>
+        <v>3.0868</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3086</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7804</v>
+        <v>3.0868</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8064</v>
+        <v>3.0868</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3086</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.115</v>
+        <v>3.0868</v>
       </c>
       <c r="N16" t="n">
-        <v>322</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.0868</v>
+        <v>3.0749</v>
       </c>
       <c r="C17" t="n">
-        <v>1.919</v>
+        <v>1.9116</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8256</v>
+        <v>0.7811</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0868</v>
+        <v>3.0749</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0868</v>
+        <v>0.8105</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0868</v>
+        <v>0.8105</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0868</v>
+        <v>0.8105</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="K17" t="n">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0868</v>
+        <v>3.0749</v>
       </c>
       <c r="N17" t="n">
-        <v>203</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0803</v>
+        <v>3.0683</v>
       </c>
       <c r="C18" t="n">
-        <v>1.915</v>
+        <v>1.9075</v>
       </c>
       <c r="D18" t="n">
-        <v>0.823</v>
+        <v>0.7785</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0803</v>
+        <v>3.0683</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0803</v>
+        <v>2.7597</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3086</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0803</v>
+        <v>2.7597</v>
       </c>
       <c r="I18" t="n">
-        <v>3.109</v>
+        <v>2.8064</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3086</v>
       </c>
       <c r="K18" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>3.109</v>
+        <v>3.115</v>
       </c>
       <c r="N18" t="n">
-        <v>245</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0749</v>
+        <v>3.0573</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9116</v>
+        <v>1.9007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8208</v>
+        <v>0.7741</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0749</v>
+        <v>3.0573</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8105</v>
+        <v>3.0573</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8105</v>
+        <v>3.0573</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8105</v>
+        <v>3.109</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="L19" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.0749</v>
+        <v>3.109</v>
       </c>
       <c r="N19" t="n">
-        <v>333</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20">
@@ -1330,7 +1330,7 @@
         <v>1.873</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7957</v>
+        <v>0.7564</v>
       </c>
       <c r="E20" t="n">
         <v>3.0128</v>
@@ -1376,7 +1376,7 @@
         <v>1.7991</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7477</v>
+        <v>0.7091</v>
       </c>
       <c r="E21" t="n">
         <v>2.894</v>
@@ -1422,7 +1422,7 @@
         <v>1.7943</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7446</v>
+        <v>0.706</v>
       </c>
       <c r="E22" t="n">
         <v>2.8862</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8355</v>
+        <v>2.8144</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7628</v>
+        <v>1.7497</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7241</v>
+        <v>0.6773</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8355</v>
+        <v>2.8144</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8355</v>
+        <v>2.8144</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8355</v>
+        <v>2.8144</v>
       </c>
       <c r="I23" t="n">
         <v>2.8619</v>
@@ -1514,7 +1514,7 @@
         <v>1.4376</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5128</v>
+        <v>0.4774</v>
       </c>
       <c r="E24" t="n">
         <v>2.3125</v>
@@ -1560,7 +1560,7 @@
         <v>1.3642</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4651</v>
+        <v>0.4303</v>
       </c>
       <c r="E25" t="n">
         <v>2.1943</v>
@@ -1606,7 +1606,7 @@
         <v>1.3415</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4503</v>
+        <v>0.4158</v>
       </c>
       <c r="E26" t="n">
         <v>2.1578</v>
@@ -1652,7 +1652,7 @@
         <v>1.3117</v>
       </c>
       <c r="D27" t="n">
-        <v>0.431</v>
+        <v>0.3967</v>
       </c>
       <c r="E27" t="n">
         <v>2.1099</v>
@@ -1698,7 +1698,7 @@
         <v>1.1808</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3459</v>
+        <v>0.3128</v>
       </c>
       <c r="E28" t="n">
         <v>1.8993</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8361</v>
+        <v>1.8224</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1415</v>
+        <v>1.1329</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3204</v>
+        <v>0.2821</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8361</v>
+        <v>1.8224</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8361</v>
+        <v>1.8224</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8361</v>
+        <v>1.8224</v>
       </c>
       <c r="I29" t="n">
         <v>1.8532</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8259</v>
+        <v>1.8088</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1351</v>
+        <v>1.1245</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3163</v>
+        <v>0.2767</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8259</v>
+        <v>1.8088</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2993</v>
+        <v>2.2822</v>
       </c>
       <c r="G30" t="n">
         <v>-0.4734</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2993</v>
+        <v>2.2822</v>
       </c>
       <c r="I30" t="n">
         <v>2.3208</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8191</v>
+        <v>1.8076</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1309</v>
+        <v>1.1237</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3135</v>
+        <v>0.2762</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8191</v>
+        <v>1.8076</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8191</v>
+        <v>2.5739</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.7663</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8191</v>
+        <v>2.5739</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8361</v>
+        <v>2.0862</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.7663</v>
       </c>
       <c r="K31" t="n">
-        <v>294</v>
+        <v>166</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8361</v>
+        <v>1.3199</v>
       </c>
       <c r="N31" t="n">
-        <v>294</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8076</v>
+        <v>1.8056</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1237</v>
+        <v>1.1225</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3089</v>
+        <v>0.2754</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8076</v>
+        <v>1.8056</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5739</v>
+        <v>1.8056</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7663</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.5739</v>
+        <v>1.8056</v>
       </c>
       <c r="I32" t="n">
-        <v>2.0862</v>
+        <v>1.8361</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7663</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="L32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3199</v>
+        <v>1.8361</v>
       </c>
       <c r="N32" t="n">
-        <v>208</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33">
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.7648</v>
+        <v>1.7562</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0971</v>
+        <v>1.0918</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2916</v>
+        <v>0.2558</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7648</v>
+        <v>1.7562</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7708</v>
+        <v>0.7622</v>
       </c>
       <c r="G33" t="n">
         <v>0.994</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7708</v>
+        <v>0.7622</v>
       </c>
       <c r="I33" t="n">
         <v>0.7816</v>
@@ -1974,7 +1974,7 @@
         <v>0.9436</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1918</v>
+        <v>0.1608</v>
       </c>
       <c r="E34" t="n">
         <v>1.5179</v>
@@ -2020,7 +2020,7 @@
         <v>0.8741</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1467</v>
+        <v>0.1163</v>
       </c>
       <c r="E35" t="n">
         <v>1.4061</v>
@@ -2066,7 +2066,7 @@
         <v>0.6823</v>
       </c>
       <c r="D36" t="n">
-        <v>0.022</v>
+        <v>-0.0067</v>
       </c>
       <c r="E36" t="n">
         <v>1.0975</v>
@@ -2112,7 +2112,7 @@
         <v>0.6492</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0005</v>
+        <v>-0.0279</v>
       </c>
       <c r="E37" t="n">
         <v>1.0442</v>
@@ -2158,7 +2158,7 @@
         <v>0.5249</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0803</v>
+        <v>-0.1075</v>
       </c>
       <c r="E38" t="n">
         <v>0.8443000000000001</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7798</v>
+        <v>0.774</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4848</v>
+        <v>0.4812</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1063</v>
+        <v>-0.1355</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7798</v>
+        <v>0.774</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7798</v>
+        <v>0.774</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7798</v>
+        <v>0.774</v>
       </c>
       <c r="I39" t="n">
         <v>0.7871</v>
@@ -2250,7 +2250,7 @@
         <v>0.4733</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1138</v>
+        <v>-0.1406</v>
       </c>
       <c r="E40" t="n">
         <v>0.7613</v>
@@ -2296,7 +2296,7 @@
         <v>0.3518</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1928</v>
+        <v>-0.2185</v>
       </c>
       <c r="E41" t="n">
         <v>0.5659</v>
@@ -2342,7 +2342,7 @@
         <v>0.2578</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2538</v>
+        <v>-0.2787</v>
       </c>
       <c r="E42" t="n">
         <v>0.4147</v>
@@ -2388,7 +2388,7 @@
         <v>0.2294</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2723</v>
+        <v>-0.2969</v>
       </c>
       <c r="E43" t="n">
         <v>0.369</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3404</v>
+        <v>0.3379</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2116</v>
+        <v>0.2101</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2838</v>
+        <v>-0.3093</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3404</v>
+        <v>0.3379</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3404</v>
+        <v>0.3379</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3404</v>
+        <v>0.3379</v>
       </c>
       <c r="I44" t="n">
         <v>0.3436</v>
@@ -2480,7 +2480,7 @@
         <v>0.1955</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2944</v>
+        <v>-0.3187</v>
       </c>
       <c r="E45" t="n">
         <v>0.3144</v>
@@ -2526,7 +2526,7 @@
         <v>0.176</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.307</v>
+        <v>-0.3311</v>
       </c>
       <c r="E46" t="n">
         <v>0.2831</v>
@@ -2572,7 +2572,7 @@
         <v>0.0839</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3669</v>
+        <v>-0.3902</v>
       </c>
       <c r="E47" t="n">
         <v>0.1349</v>
@@ -2618,7 +2618,7 @@
         <v>0.0653</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3789</v>
+        <v>-0.402</v>
       </c>
       <c r="E48" t="n">
         <v>0.1051</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0456</v>
+        <v>0.0453</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3917</v>
+        <v>-0.4149</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I49" t="n">
         <v>0.0741</v>
@@ -2710,7 +2710,7 @@
         <v>0.0324</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4003</v>
+        <v>-0.4232</v>
       </c>
       <c r="E50" t="n">
         <v>0.0521</v>
@@ -2756,7 +2756,7 @@
         <v>0.0265</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4041</v>
+        <v>-0.4269</v>
       </c>
       <c r="E51" t="n">
         <v>0.0427</v>
@@ -2802,7 +2802,7 @@
         <v>0.0148</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4117</v>
+        <v>-0.4344</v>
       </c>
       <c r="E52" t="n">
         <v>0.0238</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0329</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4427</v>
+        <v>-0.465</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0529</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0392</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4469</v>
+        <v>-0.469</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0631</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0517</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.455</v>
+        <v>-0.4771</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0832</v>
@@ -2986,7 +2986,7 @@
         <v>-0.091</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4805</v>
+        <v>-0.5022</v>
       </c>
       <c r="E56" t="n">
         <v>-0.1463</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1093</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4924</v>
+        <v>-0.5139</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1758</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1124</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4944</v>
+        <v>-0.5159</v>
       </c>
       <c r="E58" t="n">
         <v>-0.1808</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2278</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5694</v>
+        <v>-0.5899</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3665</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3193</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6288</v>
+        <v>-0.6485</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5135999999999999</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3291</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6352</v>
+        <v>-0.6548</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5293</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3417</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6434</v>
+        <v>-0.6629</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5497</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4637</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7227</v>
+        <v>-0.7411</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7459</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4737</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7292</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7619</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5348000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7689</v>
+        <v>-0.7866</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8602</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.895</v>
+        <v>-0.8958</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5564</v>
+        <v>-0.5569</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7829</v>
+        <v>-0.8008</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.895</v>
+        <v>-0.8958</v>
       </c>
       <c r="F66" t="n">
-        <v>0.105</v>
+        <v>0.1042</v>
       </c>
       <c r="G66" t="n">
         <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>0.105</v>
+        <v>0.1042</v>
       </c>
       <c r="I66" t="n">
         <v>0.1059</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5661</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7892</v>
+        <v>-0.8067</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9106</v>
@@ -3538,7 +3538,7 @@
         <v>-0.617</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8223</v>
+        <v>-0.8393</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9923999999999999</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6935</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.872</v>
+        <v>-0.8884</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1156</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7024</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8778</v>
+        <v>-0.8941</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1299</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7225</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8909</v>
+        <v>-0.9069</v>
       </c>
       <c r="E71" t="n">
         <v>-1.1622</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.2832</v>
+        <v>-1.2797</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7977</v>
+        <v>-0.7956</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9397</v>
+        <v>-0.9537</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2832</v>
+        <v>-1.2797</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.4693</v>
+        <v>-0.4658</v>
       </c>
       <c r="G72" t="n">
         <v>-0.8139</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.4693</v>
+        <v>-0.4658</v>
       </c>
       <c r="I72" t="n">
         <v>-0.4737</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8048</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9444</v>
+        <v>-0.9597</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2946</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8121</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.9643</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3063</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9802</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0583</v>
+        <v>-1.0721</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5767</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9816</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0592</v>
+        <v>-1.0729</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5789</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0201</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0842</v>
+        <v>-1.0976</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6408</v>
@@ -3998,7 +3998,7 @@
         <v>-1.0919</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1309</v>
+        <v>-1.1437</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7564</v>
@@ -4044,7 +4044,7 @@
         <v>-1.1584</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1741</v>
+        <v>-1.1862</v>
       </c>
       <c r="E79" t="n">
         <v>-1.8633</v>
@@ -4090,7 +4090,7 @@
         <v>-1.1898</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1945</v>
+        <v>-1.2064</v>
       </c>
       <c r="E80" t="n">
         <v>-1.9139</v>
@@ -4136,7 +4136,7 @@
         <v>-1.8173</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6023</v>
+        <v>-1.6085</v>
       </c>
       <c r="E81" t="n">
         <v>-2.9232</v>
